--- a/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_flash_naive.xlsx
+++ b/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_flash_naive.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.4385 ± 1.0957</t>
+          <t>9.2154 ± 4.7857</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.2009 ± 0.5923</t>
+          <t>10.8583 ± 5.7546</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8662 ± 0.0936</t>
+          <t>0.6462 ± 0.3255</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,38 +521,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C2" t="n">
-        <v>7.213333333333335</v>
+        <v>15.01930769230769</v>
       </c>
       <c r="D2" t="n">
-        <v>7.619672083932922</v>
+        <v>16.0257960080711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.2248062015503876</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14.49756097560976</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.44998717694049</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9012345679012346</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.208727272727274</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.702375650112433</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2407407407407407</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.689999999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12.56977361354023</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.213333333333335</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.619672083932922</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9324324324324325</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>51</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C7" t="n">
         <v>5.663725490196079</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D7" t="n">
         <v>6.782044489015123</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E7" t="n">
         <v>0.8</v>
       </c>
     </row>
